--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,6 +906,210 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125679581</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vinnarån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>552924</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6741894</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125679580</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vinnarån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552879</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6741877</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125654441</v>
+        <v>125654587</v>
       </c>
       <c r="B2" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552807</v>
+        <v>552771</v>
       </c>
       <c r="R2" t="n">
-        <v>6741918</v>
+        <v>6741916</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125654587</v>
+        <v>125654441</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +793,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552771</v>
+        <v>552807</v>
       </c>
       <c r="R3" t="n">
-        <v>6741916</v>
+        <v>6741918</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,11 +903,6 @@
       <c r="B4" t="n">
         <v>8447</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1015,11 +1000,6 @@
       <c r="B5" t="n">
         <v>8447</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1109,6 +1089,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125654038</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92502</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552966</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6741917</v>
+      </c>
+      <c r="S6" t="n">
+        <v>13</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125654587</v>
+        <v>125654441</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552771</v>
+        <v>552807</v>
       </c>
       <c r="R2" t="n">
-        <v>6741916</v>
+        <v>6741918</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125654441</v>
+        <v>125654587</v>
       </c>
       <c r="B3" t="n">
-        <v>92502</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,46 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552807</v>
+        <v>552771</v>
       </c>
       <c r="R3" t="n">
-        <v>6741918</v>
+        <v>6741916</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1095,7 +1095,7 @@
         <v>125654038</v>
       </c>
       <c r="B6" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125654441</v>
       </c>
       <c r="B2" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>125654038</v>
       </c>
       <c r="B6" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125654441</v>
+        <v>125654587</v>
       </c>
       <c r="B2" t="n">
-        <v>92518</v>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552807</v>
+        <v>552771</v>
       </c>
       <c r="R2" t="n">
-        <v>6741918</v>
+        <v>6741916</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125654587</v>
+        <v>125654441</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>92518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +793,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552771</v>
+        <v>552807</v>
       </c>
       <c r="R3" t="n">
-        <v>6741916</v>
+        <v>6741918</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125654441</v>
       </c>
       <c r="B3" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>125654038</v>
       </c>
       <c r="B6" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125654587</v>
+        <v>125654441</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>92522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552771</v>
+        <v>552807</v>
       </c>
       <c r="R2" t="n">
-        <v>6741916</v>
+        <v>6741918</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125654441</v>
+        <v>125654587</v>
       </c>
       <c r="B3" t="n">
-        <v>92522</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,46 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552807</v>
+        <v>552771</v>
       </c>
       <c r="R3" t="n">
-        <v>6741918</v>
+        <v>6741916</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125654441</v>
+        <v>125654587</v>
       </c>
       <c r="B2" t="n">
-        <v>92522</v>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552807</v>
+        <v>552771</v>
       </c>
       <c r="R2" t="n">
-        <v>6741918</v>
+        <v>6741916</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125654587</v>
+        <v>125654441</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>92522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +793,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552771</v>
+        <v>552807</v>
       </c>
       <c r="R3" t="n">
-        <v>6741916</v>
+        <v>6741918</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125654441</v>
       </c>
       <c r="B3" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>125654038</v>
       </c>
       <c r="B6" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125654587</v>
+        <v>125654441</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>92524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552771</v>
+        <v>552807</v>
       </c>
       <c r="R2" t="n">
-        <v>6741916</v>
+        <v>6741918</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125654441</v>
+        <v>125654587</v>
       </c>
       <c r="B3" t="n">
-        <v>92524</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,46 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skvaterbäcken, Skvaterbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552807</v>
+        <v>552771</v>
       </c>
       <c r="R3" t="n">
-        <v>6741918</v>
+        <v>6741916</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125654441</v>
       </c>
       <c r="B2" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>125654038</v>
       </c>
       <c r="B6" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125654441</v>
       </c>
       <c r="B2" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Anna-Britt Olsson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
         <v>125654038</v>
       </c>
       <c r="B6" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24821-2025 artfynd.xlsx
+++ b/artfynd/A 24821-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125654441</v>
       </c>
       <c r="B2" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>125654038</v>
       </c>
       <c r="B6" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
